--- a/CAPACITORGOODpuget/project/Summary.xlsx
+++ b/CAPACITORGOODpuget/project/Summary.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="354">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -98,49 +98,49 @@
     <t>(!!! MUST FIX !!! - not allowed)</t>
   </si>
   <si>
+    <t>Floating pin V_GNDx.MINUS(0)</t>
+  </si>
+  <si>
+    <t>Floating pin VI__CAPGD.PLUS(59)</t>
+  </si>
+  <si>
+    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
+  </si>
+  <si>
+    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
+  </si>
+  <si>
+    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
+  </si>
+  <si>
+    <t>Floating Outputs</t>
+  </si>
+  <si>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
     <t>XCAPACITORGOODpuget1,XDEBUG</t>
   </si>
   <si>
-    <t>Floating pin XDEBUG.dft_startup(dft_startup)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_capdetect(dft_capdetect)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.dft_risedelay(dft_risedelay)</t>
-  </si>
-  <si>
-    <t>Floating pin XDEBUG.DFT_CAPREFinput(DFT_CAPREFinput)</t>
-  </si>
-  <si>
-    <t>Floating pin V_GNDx.MINUS(0)</t>
-  </si>
-  <si>
-    <t>Floating pin VI__CAPGD.PLUS(59)</t>
-  </si>
-  <si>
-    <t>Xsim_CAPACITORGOODpuget_ROW8</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.ok_capacitorgood(ok_capacitorgood)</t>
-  </si>
-  <si>
-    <t>Floating pin XCAPACITORGOODpuget1.status_chrg_status_xdatamap1_6aa5ac6c(status_chrg_status_xdatamap1_6aa5ac6c)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.GND(GND)</t>
-  </si>
-  <si>
-    <t>Floating pin XFORCE_CAPACITORGOODpuget1.register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d(register_enable_capacitorgood_xd_enable_capacitorgood_32c14a0d)</t>
-  </si>
-  <si>
-    <t>Floating Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Customer</t>
-  </si>
-  <si>
-    <t>No Connects - Celera</t>
+    <t>XDEBUG.dft_startup net: dft_startup io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_capdetect net: dft_capdetect io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.dft_risedelay net: dft_risedelay io: input</t>
+  </si>
+  <si>
+    <t>XDEBUG.DFT_CAPREFinput net: DFT_CAPREFinput io: input</t>
   </si>
   <si>
     <t>XIP.IN net: noconn_IN io: output</t>
@@ -1066,6 +1066,9 @@
   </si>
   <si>
     <t>9</t>
+  </si>
+  <si>
+    <t>noconn</t>
   </si>
   <si>
     <t>dbuf</t>
@@ -3371,7 +3374,7 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -3421,7 +3424,7 @@
         <v>342</v>
       </c>
       <c r="B8" t="s">
-        <v>201</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -3429,7 +3432,7 @@
         <v>343</v>
       </c>
       <c r="B9" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -3445,7 +3448,7 @@
         <v>345</v>
       </c>
       <c r="B11" t="s">
-        <v>326</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -3501,6 +3504,14 @@
         <v>352</v>
       </c>
       <c r="B18" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B19" t="s">
         <v>326</v>
       </c>
     </row>
@@ -3586,7 +3597,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3606,32 +3617,32 @@
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:1">
@@ -3642,31 +3653,6 @@
     <row r="15" spans="1:1">
       <c r="A15" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3676,42 +3662,42 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" t="s">
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -3722,31 +3708,6 @@
     <row r="12" spans="1:1">
       <c r="A12" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -3761,7 +3722,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3776,21 +3737,46 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
         <v>34</v>
       </c>
     </row>

--- a/CAPACITORGOODpuget/project/Summary.xlsx
+++ b/CAPACITORGOODpuget/project/Summary.xlsx
@@ -306,6 +306,9 @@
     <t>dft_ignore_bricks</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>dft_measure</t>
   </si>
   <si>
@@ -373,9 +376,6 @@
   </si>
   <si>
     <t>serdes_memory_bist</t>
-  </si>
-  <si>
-    <t>Y</t>
   </si>
   <si>
     <t>serdes_address</t>
@@ -1922,12 +1922,12 @@
         <v>86</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B8" t="s">
         <v>84</v>
@@ -1935,31 +1935,31 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" t="s">
         <v>92</v>
-      </c>
-      <c r="B11" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1967,32 +1967,32 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2005,7 +2005,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B20" t="s">
         <v>84</v>
@@ -2013,15 +2013,15 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B21" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2034,12 +2034,12 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2052,7 +2052,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
         <v>84</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
         <v>84</v>
@@ -2068,18 +2068,18 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2087,7 +2087,7 @@
         <v>111</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2095,7 +2095,7 @@
         <v>112</v>
       </c>
       <c r="B32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2156,7 +2156,7 @@
         <v>124</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2164,7 +2164,7 @@
         <v>125</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -2172,7 +2172,7 @@
         <v>126</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>136</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>139</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2458,7 +2458,7 @@
         <v>174</v>
       </c>
       <c r="B83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -2466,7 +2466,7 @@
         <v>175</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -2474,7 +2474,7 @@
         <v>176</v>
       </c>
       <c r="B85" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -2482,7 +2482,7 @@
         <v>177</v>
       </c>
       <c r="B86" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -2490,7 +2490,7 @@
         <v>178</v>
       </c>
       <c r="B87" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -2498,7 +2498,7 @@
         <v>179</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -2506,7 +2506,7 @@
         <v>180</v>
       </c>
       <c r="B89" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -2514,7 +2514,7 @@
         <v>181</v>
       </c>
       <c r="B90" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -2530,7 +2530,7 @@
         <v>184</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -2554,7 +2554,7 @@
         <v>187</v>
       </c>
       <c r="B95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -2562,7 +2562,7 @@
         <v>188</v>
       </c>
       <c r="B96" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -2570,7 +2570,7 @@
         <v>189</v>
       </c>
       <c r="B97" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -2578,7 +2578,7 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -2586,7 +2586,7 @@
         <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -2594,7 +2594,7 @@
         <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -2602,7 +2602,7 @@
         <v>193</v>
       </c>
       <c r="B101" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -3188,7 +3188,7 @@
         <v>310</v>
       </c>
       <c r="B175" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="176" spans="1:2">
